--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/79.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/79.xlsx
@@ -426,13 +426,13 @@
         <v>-8.756288524297199</v>
       </c>
       <c r="E2">
-        <v>-6.291587626050329</v>
+        <v>-4.892003863817705</v>
       </c>
       <c r="F2">
-        <v>-5.15056251355387</v>
+        <v>-5.11978038086584</v>
       </c>
       <c r="G2">
-        <v>-6.523351682709266</v>
+        <v>-6.565253257599821</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.88046163916106</v>
       </c>
       <c r="E3">
-        <v>-7.239293080953559</v>
+        <v>-5.812710556687204</v>
       </c>
       <c r="F3">
-        <v>-5.092783058841201</v>
+        <v>-5.257364751164213</v>
       </c>
       <c r="G3">
-        <v>-6.681595759486428</v>
+        <v>-6.495427231085513</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.145011491264752</v>
       </c>
       <c r="E4">
-        <v>-7.445949992293595</v>
+        <v>-6.233061627975197</v>
       </c>
       <c r="F4">
-        <v>-5.551148564036668</v>
+        <v>-5.389308767816924</v>
       </c>
       <c r="G4">
-        <v>-6.50479938550719</v>
+        <v>-6.584689470460882</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.509653725461565</v>
       </c>
       <c r="E5">
-        <v>-8.080633738364627</v>
+        <v>-6.915421148398982</v>
       </c>
       <c r="F5">
-        <v>-5.416857782531826</v>
+        <v>-5.28596247901106</v>
       </c>
       <c r="G5">
-        <v>-6.598769220639403</v>
+        <v>-6.660368541488621</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.941546443017362</v>
       </c>
       <c r="E6">
-        <v>-9.730977220297989</v>
+        <v>-7.776279528783109</v>
       </c>
       <c r="F6">
-        <v>-5.375040967671104</v>
+        <v>-4.956583718840309</v>
       </c>
       <c r="G6">
-        <v>-6.156463783865076</v>
+        <v>-6.367388571808661</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.38642324848976</v>
       </c>
       <c r="E7">
-        <v>-9.477287577914288</v>
+        <v>-9.693608252786692</v>
       </c>
       <c r="F7">
-        <v>-5.52238764781147</v>
+        <v>-5.280830742950717</v>
       </c>
       <c r="G7">
-        <v>-6.027431960926442</v>
+        <v>-6.811885589729985</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.80733679934235</v>
       </c>
       <c r="E8">
-        <v>-11.13074212149092</v>
+        <v>-10.23012373931945</v>
       </c>
       <c r="F8">
-        <v>-5.319015995117566</v>
+        <v>-5.017563156829992</v>
       </c>
       <c r="G8">
-        <v>-6.191168232753255</v>
+        <v>-6.402712092712684</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.16401883964209</v>
       </c>
       <c r="E9">
-        <v>-11.6448960033738</v>
+        <v>-9.948805877014948</v>
       </c>
       <c r="F9">
-        <v>-5.033992995897117</v>
+        <v>-4.799666081727999</v>
       </c>
       <c r="G9">
-        <v>-6.124301833951056</v>
+        <v>-5.951077538608691</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.42030200768664</v>
       </c>
       <c r="E10">
-        <v>-12.06774226384002</v>
+        <v>-10.90317271718346</v>
       </c>
       <c r="F10">
-        <v>-5.138166823738378</v>
+        <v>-5.018900141818111</v>
       </c>
       <c r="G10">
-        <v>-6.414385076284154</v>
+        <v>-5.43715507018331</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.5598820334289</v>
       </c>
       <c r="E11">
-        <v>-12.53548834409229</v>
+        <v>-12.20611431561839</v>
       </c>
       <c r="F11">
-        <v>-4.868488502287387</v>
+        <v>-4.674725911465957</v>
       </c>
       <c r="G11">
-        <v>-5.668300670280764</v>
+        <v>-5.642379098708271</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.57199376244354</v>
       </c>
       <c r="E12">
-        <v>-14.44640474890101</v>
+        <v>-13.70034318461133</v>
       </c>
       <c r="F12">
-        <v>-4.635801755575812</v>
+        <v>-4.836201226028471</v>
       </c>
       <c r="G12">
-        <v>-5.212087631695959</v>
+        <v>-5.517458973329411</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.45244013224062</v>
       </c>
       <c r="E13">
-        <v>-13.94815486773307</v>
+        <v>-14.57944678677236</v>
       </c>
       <c r="F13">
-        <v>-4.442773098273262</v>
+        <v>-4.305906922513117</v>
       </c>
       <c r="G13">
-        <v>-4.817682478329346</v>
+        <v>-4.761138360518594</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.21895823244982</v>
       </c>
       <c r="E14">
-        <v>-15.14002658418187</v>
+        <v>-14.42983506250694</v>
       </c>
       <c r="F14">
-        <v>-4.261766537087543</v>
+        <v>-4.144940225535922</v>
       </c>
       <c r="G14">
-        <v>-4.937851970859351</v>
+        <v>-4.171430883608219</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.88961616237514</v>
       </c>
       <c r="E15">
-        <v>-16.36663622474351</v>
+        <v>-16.10503533826841</v>
       </c>
       <c r="F15">
-        <v>-4.459617949409191</v>
+        <v>-4.176588002159878</v>
       </c>
       <c r="G15">
-        <v>-4.148502045203226</v>
+        <v>-4.109381328565658</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.49007231137393</v>
       </c>
       <c r="E16">
-        <v>-17.11664661836788</v>
+        <v>-17.14214192703107</v>
       </c>
       <c r="F16">
-        <v>-3.918272396373089</v>
+        <v>-3.888741926830689</v>
       </c>
       <c r="G16">
-        <v>-3.664821410279088</v>
+        <v>-3.062772219598308</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.05802385715714</v>
       </c>
       <c r="E17">
-        <v>-18.79656103557133</v>
+        <v>-17.66358665206629</v>
       </c>
       <c r="F17">
-        <v>-3.959646863040716</v>
+        <v>-3.68671802790114</v>
       </c>
       <c r="G17">
-        <v>-2.470558659714703</v>
+        <v>-2.996846015729262</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.621959526990414</v>
       </c>
       <c r="E18">
-        <v>-18.94475081899834</v>
+        <v>-18.76434547148076</v>
       </c>
       <c r="F18">
-        <v>-3.415283567556215</v>
+        <v>-3.443880467035659</v>
       </c>
       <c r="G18">
-        <v>-3.585106784238977</v>
+        <v>-2.729320830700757</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.212584881083451</v>
       </c>
       <c r="E19">
-        <v>-19.89884142225238</v>
+        <v>-20.29793583654837</v>
       </c>
       <c r="F19">
-        <v>-3.396564120987752</v>
+        <v>-2.992962813158762</v>
       </c>
       <c r="G19">
-        <v>-2.801921094376974</v>
+        <v>-2.262845100944211</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.859152848578166</v>
       </c>
       <c r="E20">
-        <v>-20.34537613025272</v>
+        <v>-20.51904310844688</v>
       </c>
       <c r="F20">
-        <v>-3.161615931266533</v>
+        <v>-2.780481604136272</v>
       </c>
       <c r="G20">
-        <v>-2.38308742547608</v>
+        <v>-2.541867810630605</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.57217071122537</v>
       </c>
       <c r="E21">
-        <v>-21.24763382001497</v>
+        <v>-21.94112432954961</v>
       </c>
       <c r="F21">
-        <v>-2.771574169453969</v>
+        <v>-2.663961788523688</v>
       </c>
       <c r="G21">
-        <v>-2.479315052666076</v>
+        <v>-1.823015952233259</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.362924940655745</v>
       </c>
       <c r="E22">
-        <v>-22.5757854332506</v>
+        <v>-22.12964017401492</v>
       </c>
       <c r="F22">
-        <v>-2.804218472063492</v>
+        <v>-2.476003568093675</v>
       </c>
       <c r="G22">
-        <v>-2.704620850432255</v>
+        <v>-1.502392927300384</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.232140520708258</v>
       </c>
       <c r="E23">
-        <v>-22.5472107622622</v>
+        <v>-22.62148226446201</v>
       </c>
       <c r="F23">
-        <v>-2.816080693271581</v>
+        <v>-2.459340957786363</v>
       </c>
       <c r="G23">
-        <v>-2.51927002677954</v>
+        <v>-2.21960937620133</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.164067445601772</v>
       </c>
       <c r="E24">
-        <v>-23.73721221894584</v>
+        <v>-23.89856627631314</v>
       </c>
       <c r="F24">
-        <v>-2.42545990264446</v>
+        <v>-2.033435029269594</v>
       </c>
       <c r="G24">
-        <v>-2.646219516573972</v>
+        <v>-1.812269921412785</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.148830469261236</v>
       </c>
       <c r="E25">
-        <v>-22.43452874352934</v>
+        <v>-24.50087596170334</v>
       </c>
       <c r="F25">
-        <v>-2.60580376990794</v>
+        <v>-2.147155791428119</v>
       </c>
       <c r="G25">
-        <v>-3.000709422373591</v>
+        <v>-2.165409124632382</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.167045805910213</v>
       </c>
       <c r="E26">
-        <v>-24.71761778465845</v>
+        <v>-24.49877927823778</v>
       </c>
       <c r="F26">
-        <v>-2.046057691753453</v>
+        <v>-1.576476920291483</v>
       </c>
       <c r="G26">
-        <v>-3.058432094396324</v>
+        <v>-2.292987618079275</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.191983302028792</v>
       </c>
       <c r="E27">
-        <v>-24.85870239236742</v>
+        <v>-23.97372988789245</v>
       </c>
       <c r="F27">
-        <v>-2.254013529654449</v>
+        <v>-1.945080533719596</v>
       </c>
       <c r="G27">
-        <v>-3.872998445425078</v>
+        <v>-2.291415108948122</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.210427713963387</v>
       </c>
       <c r="E28">
-        <v>-23.77680013872089</v>
+        <v>-24.04999844712964</v>
       </c>
       <c r="F28">
-        <v>-2.439094001727137</v>
+        <v>-1.9636343068075</v>
       </c>
       <c r="G28">
-        <v>-3.336901942977659</v>
+        <v>-2.321114012980924</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.202551813520394</v>
       </c>
       <c r="E29">
-        <v>-24.31933849568384</v>
+        <v>-24.56930120395923</v>
       </c>
       <c r="F29">
-        <v>-2.393751655200101</v>
+        <v>-1.998680874885141</v>
       </c>
       <c r="G29">
-        <v>-3.175632027577602</v>
+        <v>-3.056564946712175</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.149950333352635</v>
       </c>
       <c r="E30">
-        <v>-23.41503393567013</v>
+        <v>-23.96942330911116</v>
       </c>
       <c r="F30">
-        <v>-2.468694882498775</v>
+        <v>-1.762905974495929</v>
       </c>
       <c r="G30">
-        <v>-2.94666145589945</v>
+        <v>-2.793124974879131</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.047063496908461</v>
       </c>
       <c r="E31">
-        <v>-23.73338112993535</v>
+        <v>-23.84521632402877</v>
       </c>
       <c r="F31">
-        <v>-2.473955843873954</v>
+        <v>-2.122845693258161</v>
       </c>
       <c r="G31">
-        <v>-3.618212239631689</v>
+        <v>-2.664477175223052</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.8865801954961</v>
       </c>
       <c r="E32">
-        <v>-23.18977858158059</v>
+        <v>-23.91887648223754</v>
       </c>
       <c r="F32">
-        <v>-2.528416858771008</v>
+        <v>-2.119345840981333</v>
       </c>
       <c r="G32">
-        <v>-3.434447167292284</v>
+        <v>-2.756123007386697</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.670700322529184</v>
       </c>
       <c r="E33">
-        <v>-22.00112208167723</v>
+        <v>-23.97549146428144</v>
       </c>
       <c r="F33">
-        <v>-2.312707501979808</v>
+        <v>-1.951962610102054</v>
       </c>
       <c r="G33">
-        <v>-3.391320690552199</v>
+        <v>-2.823207902194488</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.411958384416839</v>
       </c>
       <c r="E34">
-        <v>-22.80316011317573</v>
+        <v>-22.9486101698281</v>
       </c>
       <c r="F34">
-        <v>-2.443479378757558</v>
+        <v>-2.161367262590547</v>
       </c>
       <c r="G34">
-        <v>-3.496351058331116</v>
+        <v>-2.382494837824551</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.120387011996044</v>
       </c>
       <c r="E35">
-        <v>-22.40086406775632</v>
+        <v>-22.87341485893073</v>
       </c>
       <c r="F35">
-        <v>-2.501566157776665</v>
+        <v>-2.212353276232856</v>
       </c>
       <c r="G35">
-        <v>-2.862828511208486</v>
+        <v>-3.015116916560499</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.815663683978136</v>
       </c>
       <c r="E36">
-        <v>-20.94565253081348</v>
+        <v>-22.00929597726108</v>
       </c>
       <c r="F36">
-        <v>-2.574031738173566</v>
+        <v>-2.187202385149058</v>
       </c>
       <c r="G36">
-        <v>-3.485168035499458</v>
+        <v>-1.804486828849958</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.518956620236953</v>
       </c>
       <c r="E37">
-        <v>-21.511553285182</v>
+        <v>-21.61234353117072</v>
       </c>
       <c r="F37">
-        <v>-2.369037313737577</v>
+        <v>-2.153495287161743</v>
       </c>
       <c r="G37">
-        <v>-3.502843038133627</v>
+        <v>-2.512854189524432</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.244065269292999</v>
       </c>
       <c r="E38">
-        <v>-20.1640560309856</v>
+        <v>-21.20378913467271</v>
       </c>
       <c r="F38">
-        <v>-2.452332141191276</v>
+        <v>-2.259312595930158</v>
       </c>
       <c r="G38">
-        <v>-2.700386662687527</v>
+        <v>-2.12398757884502</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.010520914466942</v>
       </c>
       <c r="E39">
-        <v>-21.13188149590491</v>
+        <v>-21.14057163752563</v>
       </c>
       <c r="F39">
-        <v>-2.194097715409961</v>
+        <v>-2.426098573912018</v>
       </c>
       <c r="G39">
-        <v>-2.622943070887356</v>
+        <v>-1.716651434602015</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.830038166594384</v>
       </c>
       <c r="E40">
-        <v>-20.26759958917098</v>
+        <v>-20.5059467616167</v>
       </c>
       <c r="F40">
-        <v>-2.396711411930303</v>
+        <v>-2.532444381083419</v>
       </c>
       <c r="G40">
-        <v>-2.027991689842774</v>
+        <v>-1.851907083154479</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.703847597696273</v>
       </c>
       <c r="E41">
-        <v>-19.64427325591119</v>
+        <v>-19.44572231304488</v>
       </c>
       <c r="F41">
-        <v>-2.338936927422052</v>
+        <v>-2.391936702220567</v>
       </c>
       <c r="G41">
-        <v>-1.997614123974422</v>
+        <v>-1.253161816921892</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.637288321746332</v>
       </c>
       <c r="E42">
-        <v>-19.14424368445824</v>
+        <v>-18.34718697436818</v>
       </c>
       <c r="F42">
-        <v>-2.068282789170564</v>
+        <v>-2.538905646825255</v>
       </c>
       <c r="G42">
-        <v>-1.664175977259028</v>
+        <v>-1.283645320247501</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.62368272544822</v>
       </c>
       <c r="E43">
-        <v>-17.99282935479397</v>
+        <v>-19.38205196849704</v>
       </c>
       <c r="F43">
-        <v>-2.700531724255078</v>
+        <v>-2.376641726495277</v>
       </c>
       <c r="G43">
-        <v>-2.189996546352549</v>
+        <v>-1.35042233432014</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.652082174446708</v>
       </c>
       <c r="E44">
-        <v>-18.21895870436698</v>
+        <v>-17.41744597585338</v>
       </c>
       <c r="F44">
-        <v>-2.684130049679648</v>
+        <v>-2.56345182970501</v>
       </c>
       <c r="G44">
-        <v>-1.775992963393451</v>
+        <v>-0.6539630059504249</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.717337689185873</v>
       </c>
       <c r="E45">
-        <v>-17.06174339949889</v>
+        <v>-17.39481266276304</v>
       </c>
       <c r="F45">
-        <v>-2.779644953059445</v>
+        <v>-2.733186795640838</v>
       </c>
       <c r="G45">
-        <v>-1.455002467905717</v>
+        <v>-0.7684085652430299</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.805868753459237</v>
       </c>
       <c r="E46">
-        <v>-17.90402145102954</v>
+        <v>-16.57630457129865</v>
       </c>
       <c r="F46">
-        <v>-2.608032078221471</v>
+        <v>-2.483809274130254</v>
       </c>
       <c r="G46">
-        <v>-1.448705810290023</v>
+        <v>-0.2203113352157529</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.908463799957643</v>
       </c>
       <c r="E47">
-        <v>-16.5145814705741</v>
+        <v>-16.09809318761465</v>
       </c>
       <c r="F47">
-        <v>-2.773392435903114</v>
+        <v>-2.676388127933083</v>
       </c>
       <c r="G47">
-        <v>-1.547641463731143</v>
+        <v>-0.2440181518224738</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.020878473383964</v>
       </c>
       <c r="E48">
-        <v>-15.95059626071082</v>
+        <v>-15.8932567228257</v>
       </c>
       <c r="F48">
-        <v>-2.959717115814807</v>
+        <v>-2.696018778644626</v>
       </c>
       <c r="G48">
-        <v>-1.790801033590611</v>
+        <v>-0.4070724512681976</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.135199645221548</v>
       </c>
       <c r="E49">
-        <v>-14.52974225606417</v>
+        <v>-15.21999943515733</v>
       </c>
       <c r="F49">
-        <v>-2.849390174905552</v>
+        <v>-2.595660411060661</v>
       </c>
       <c r="G49">
-        <v>-2.244163692466104</v>
+        <v>-0.4690889008553648</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.257335879042606</v>
       </c>
       <c r="E50">
-        <v>-14.39427295612471</v>
+        <v>-14.37547978899287</v>
       </c>
       <c r="F50">
-        <v>-2.781870776270767</v>
+        <v>-3.080570121311435</v>
       </c>
       <c r="G50">
-        <v>-1.462520716825402</v>
+        <v>-0.2261544480925665</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.395738621102076</v>
       </c>
       <c r="E51">
-        <v>-14.53629948642727</v>
+        <v>-13.55930386164243</v>
       </c>
       <c r="F51">
-        <v>-2.70628473586752</v>
+        <v>-2.779623415506972</v>
       </c>
       <c r="G51">
-        <v>-2.427505014976481</v>
+        <v>-0.2757000726332991</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.553516614511694</v>
       </c>
       <c r="E52">
-        <v>-13.85267652175535</v>
+        <v>-13.3203544021537</v>
       </c>
       <c r="F52">
-        <v>-3.144708124207992</v>
+        <v>-2.959239147823391</v>
       </c>
       <c r="G52">
-        <v>-2.725589845877999</v>
+        <v>-0.2687843430017616</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.741957298859496</v>
       </c>
       <c r="E53">
-        <v>-14.05199730520296</v>
+        <v>-13.02127586479112</v>
       </c>
       <c r="F53">
-        <v>-3.364334002079628</v>
+        <v>-3.028624029849281</v>
       </c>
       <c r="G53">
-        <v>-1.299582286473552</v>
+        <v>-0.1653231738084585</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.962642950095901</v>
       </c>
       <c r="E54">
-        <v>-13.15919054069472</v>
+        <v>-11.717636881359</v>
       </c>
       <c r="F54">
-        <v>-3.153989980956361</v>
+        <v>-3.154870535505537</v>
       </c>
       <c r="G54">
-        <v>-1.940623082515868</v>
+        <v>-0.5171811959043573</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.209584982109129</v>
       </c>
       <c r="E55">
-        <v>-12.87304532509804</v>
+        <v>-11.5577002363561</v>
       </c>
       <c r="F55">
-        <v>-3.022295302891893</v>
+        <v>-3.263283119346922</v>
       </c>
       <c r="G55">
-        <v>-2.078649657684702</v>
+        <v>-0.3429306314448184</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.482601432353712</v>
       </c>
       <c r="E56">
-        <v>-11.91639613402966</v>
+        <v>-10.7210012648029</v>
       </c>
       <c r="F56">
-        <v>-3.156799803186657</v>
+        <v>-3.291752450246336</v>
       </c>
       <c r="G56">
-        <v>-2.100628369519923</v>
+        <v>-0.4468552770136195</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.77100949865111</v>
       </c>
       <c r="E57">
-        <v>-11.3829418959261</v>
+        <v>-11.26826734862986</v>
       </c>
       <c r="F57">
-        <v>-3.225063904116559</v>
+        <v>-3.514107798710196</v>
       </c>
       <c r="G57">
-        <v>-2.24595138705731</v>
+        <v>-0.1800981385502258</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.064784992464599</v>
       </c>
       <c r="E58">
-        <v>-11.73329634447753</v>
+        <v>-9.68403053026047</v>
       </c>
       <c r="F58">
-        <v>-2.994504404895372</v>
+        <v>-3.396976647954346</v>
       </c>
       <c r="G58">
-        <v>-2.280258570480778</v>
+        <v>-0.3656277316620616</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.362231305010535</v>
       </c>
       <c r="E59">
-        <v>-10.82300514182567</v>
+        <v>-10.07790361402561</v>
       </c>
       <c r="F59">
-        <v>-3.264008769191775</v>
+        <v>-3.464473680669255</v>
       </c>
       <c r="G59">
-        <v>-2.244385499017235</v>
+        <v>-0.3299764667496502</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.654907345300371</v>
       </c>
       <c r="E60">
-        <v>-9.734110924311295</v>
+        <v>-9.403813087139836</v>
       </c>
       <c r="F60">
-        <v>-3.44483060444667</v>
+        <v>-3.303303205310972</v>
       </c>
       <c r="G60">
-        <v>-2.211945463277917</v>
+        <v>-0.4564856539873594</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.942814853780606</v>
       </c>
       <c r="E61">
-        <v>-9.849437571864637</v>
+        <v>-8.857864789249104</v>
       </c>
       <c r="F61">
-        <v>-3.491075871442758</v>
+        <v>-3.376718094751481</v>
       </c>
       <c r="G61">
-        <v>-2.447202760935145</v>
+        <v>-1.045315836329829</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.22963911452409</v>
       </c>
       <c r="E62">
-        <v>-9.80377243997129</v>
+        <v>-8.37752955125551</v>
       </c>
       <c r="F62">
-        <v>-3.284830612228543</v>
+        <v>-3.318029092630538</v>
       </c>
       <c r="G62">
-        <v>-2.332465873635084</v>
+        <v>-0.8410485554657182</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.510308094143072</v>
       </c>
       <c r="E63">
-        <v>-9.510005802619705</v>
+        <v>-7.64850863465669</v>
       </c>
       <c r="F63">
-        <v>-3.444487660341911</v>
+        <v>-3.266117792599302</v>
       </c>
       <c r="G63">
-        <v>-3.075160281006261</v>
+        <v>-1.54551940404047</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.789823610040413</v>
       </c>
       <c r="E64">
-        <v>-9.657511786471552</v>
+        <v>-8.204913179031131</v>
       </c>
       <c r="F64">
-        <v>-3.22498438084589</v>
+        <v>-3.613786905023866</v>
       </c>
       <c r="G64">
-        <v>-2.158652301186729</v>
+        <v>-1.305501541897769</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.068689230455</v>
       </c>
       <c r="E65">
-        <v>-9.34778227824293</v>
+        <v>-8.318057102112775</v>
       </c>
       <c r="F65">
-        <v>-3.346249913309112</v>
+        <v>-3.570401990669644</v>
       </c>
       <c r="G65">
-        <v>-3.245365358816811</v>
+        <v>-1.517664473873042</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.33612362885629</v>
       </c>
       <c r="E66">
-        <v>-9.048495431075997</v>
+        <v>-7.624915285076727</v>
       </c>
       <c r="F66">
-        <v>-3.423620257097989</v>
+        <v>-3.005983920363368</v>
       </c>
       <c r="G66">
-        <v>-3.224330152460281</v>
+        <v>-1.758274923667272</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.59011623595256</v>
       </c>
       <c r="E67">
-        <v>-8.668035687321572</v>
+        <v>-6.463393401427334</v>
       </c>
       <c r="F67">
-        <v>-3.479087738389444</v>
+        <v>-3.670877986424808</v>
       </c>
       <c r="G67">
-        <v>-2.993667892011561</v>
+        <v>-1.697043073372912</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.81964324268739</v>
       </c>
       <c r="E68">
-        <v>-9.483718011005179</v>
+        <v>-7.12950022863759</v>
       </c>
       <c r="F68">
-        <v>-3.207456126602652</v>
+        <v>-3.440229023524119</v>
       </c>
       <c r="G68">
-        <v>-3.51922692800748</v>
+        <v>-1.535746673608541</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.00915315078371</v>
       </c>
       <c r="E69">
-        <v>-8.224417316582167</v>
+        <v>-6.566506754581988</v>
       </c>
       <c r="F69">
-        <v>-3.72200399415819</v>
+        <v>-3.409692087587318</v>
       </c>
       <c r="G69">
-        <v>-3.104412261391261</v>
+        <v>-1.587321662564847</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.15562051491423</v>
       </c>
       <c r="E70">
-        <v>-8.770469769375074</v>
+        <v>-6.775708668314336</v>
       </c>
       <c r="F70">
-        <v>-3.742020664079438</v>
+        <v>-3.345327112022394</v>
       </c>
       <c r="G70">
-        <v>-3.698009629310282</v>
+        <v>-1.915204713865344</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.24928167370223</v>
       </c>
       <c r="E71">
-        <v>-8.543072447079908</v>
+        <v>-6.72737626523047</v>
       </c>
       <c r="F71">
-        <v>-3.465764277082816</v>
+        <v>-3.662208293187108</v>
       </c>
       <c r="G71">
-        <v>-3.234424005809519</v>
+        <v>-2.374297927069315</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.28074099567201</v>
       </c>
       <c r="E72">
-        <v>-8.136660018787524</v>
+        <v>-6.190235849284658</v>
       </c>
       <c r="F72">
-        <v>-3.625618476638051</v>
+        <v>-3.507470090711563</v>
       </c>
       <c r="G72">
-        <v>-3.274806040297549</v>
+        <v>-1.936564353684722</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.25226804464195</v>
       </c>
       <c r="E73">
-        <v>-9.067170857883628</v>
+        <v>-7.285193693495305</v>
       </c>
       <c r="F73">
-        <v>-3.654305668164401</v>
+        <v>-3.63113374680589</v>
       </c>
       <c r="G73">
-        <v>-3.218861131229406</v>
+        <v>-1.652267944954269</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.15861885336443</v>
       </c>
       <c r="E74">
-        <v>-9.407096230795396</v>
+        <v>-6.666205638334859</v>
       </c>
       <c r="F74">
-        <v>-3.72655173119956</v>
+        <v>-3.693803882664687</v>
       </c>
       <c r="G74">
-        <v>-3.103091353721092</v>
+        <v>-1.604735132101413</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.00058003789391</v>
       </c>
       <c r="E75">
-        <v>-8.775315236563282</v>
+        <v>-7.052647496253416</v>
       </c>
       <c r="F75">
-        <v>-3.480611106043192</v>
+        <v>-3.730665403721862</v>
       </c>
       <c r="G75">
-        <v>-3.048626258509002</v>
+        <v>-1.152498058709273</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.78920528265937</v>
       </c>
       <c r="E76">
-        <v>-10.05461367220417</v>
+        <v>-7.280737675071757</v>
       </c>
       <c r="F76">
-        <v>-3.755876765626065</v>
+        <v>-4.083813338148541</v>
       </c>
       <c r="G76">
-        <v>-2.507808918122583</v>
+        <v>-0.7467112497786466</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.5302820953715</v>
       </c>
       <c r="E77">
-        <v>-8.943588802214304</v>
+        <v>-8.566774480036054</v>
       </c>
       <c r="F77">
-        <v>-3.876467178656006</v>
+        <v>-4.117908940447769</v>
       </c>
       <c r="G77">
-        <v>-1.336875581973443</v>
+        <v>-0.9042965279934942</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.24000941408949</v>
       </c>
       <c r="E78">
-        <v>-9.458824989385015</v>
+        <v>-8.756934160566148</v>
       </c>
       <c r="F78">
-        <v>-3.981367484709521</v>
+        <v>-4.119121670325468</v>
       </c>
       <c r="G78">
-        <v>-2.183170201450572</v>
+        <v>-0.845928299590604</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.937344098872829</v>
       </c>
       <c r="E79">
-        <v>-12.21901140959224</v>
+        <v>-8.855709235621454</v>
       </c>
       <c r="F79">
-        <v>-4.310155618922075</v>
+        <v>-3.814475475700102</v>
       </c>
       <c r="G79">
-        <v>-2.062404810723498</v>
+        <v>-0.0215925286754606</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.63151109526758</v>
       </c>
       <c r="E80">
-        <v>-11.2639788837446</v>
+        <v>-9.067279541259813</v>
       </c>
       <c r="F80">
-        <v>-4.206676791331764</v>
+        <v>-4.458344748711088</v>
       </c>
       <c r="G80">
-        <v>-2.299605398612278</v>
+        <v>-0.4801593651386876</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.343894245325171</v>
       </c>
       <c r="E81">
-        <v>-10.95195796766809</v>
+        <v>-9.820903657142306</v>
       </c>
       <c r="F81">
-        <v>-4.444260846128691</v>
+        <v>-4.469320616798181</v>
       </c>
       <c r="G81">
-        <v>-1.844868863337988</v>
+        <v>0.326001510765857</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.090170933103481</v>
       </c>
       <c r="E82">
-        <v>-12.77026707901996</v>
+        <v>-10.59503723180554</v>
       </c>
       <c r="F82">
-        <v>-4.574204355503641</v>
+        <v>-4.301215049543661</v>
       </c>
       <c r="G82">
-        <v>-2.168855402538763</v>
+        <v>0.4019619781644344</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.874728527170177</v>
       </c>
       <c r="E83">
-        <v>-13.46801435412181</v>
+        <v>-12.08263188637724</v>
       </c>
       <c r="F83">
-        <v>-4.513821342043974</v>
+        <v>-4.802721100709523</v>
       </c>
       <c r="G83">
-        <v>-1.914436667300233</v>
+        <v>0.4563575519201992</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.711083280159929</v>
       </c>
       <c r="E84">
-        <v>-13.50430101634527</v>
+        <v>-13.0435831277529</v>
       </c>
       <c r="F84">
-        <v>-4.503595974823816</v>
+        <v>-4.871259391249752</v>
       </c>
       <c r="G84">
-        <v>-1.334184108450015</v>
+        <v>0.5942980529050118</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.600721245358995</v>
       </c>
       <c r="E85">
-        <v>-15.37628160163604</v>
+        <v>-13.64130999744733</v>
       </c>
       <c r="F85">
-        <v>-4.925960632693617</v>
+        <v>-4.902256071095106</v>
       </c>
       <c r="G85">
-        <v>-0.9252026230739918</v>
+        <v>0.3950528696239754</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.538132391843778</v>
       </c>
       <c r="E86">
-        <v>-15.73921162250677</v>
+        <v>-15.19576757074228</v>
       </c>
       <c r="F86">
-        <v>-4.634936111639886</v>
+        <v>-5.168972150713685</v>
       </c>
       <c r="G86">
-        <v>-1.272968810883351</v>
+        <v>0.9622221525029937</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.529156970310815</v>
       </c>
       <c r="E87">
-        <v>-17.21150456340655</v>
+        <v>-16.05036760004781</v>
       </c>
       <c r="F87">
-        <v>-4.889667371674762</v>
+        <v>-5.072511251759892</v>
       </c>
       <c r="G87">
-        <v>-0.8502915986113634</v>
+        <v>0.8531131926196939</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.566976375396509</v>
       </c>
       <c r="E88">
-        <v>-18.48579450679495</v>
+        <v>-17.8662132215395</v>
       </c>
       <c r="F88">
-        <v>-5.2060523607652</v>
+        <v>-5.325228750638562</v>
       </c>
       <c r="G88">
-        <v>-0.6053939923437773</v>
+        <v>1.271973345884902</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.645178764097622</v>
       </c>
       <c r="E89">
-        <v>-20.77797219525746</v>
+        <v>-19.18717814652496</v>
       </c>
       <c r="F89">
-        <v>-5.278397827888694</v>
+        <v>-5.493632530158091</v>
       </c>
       <c r="G89">
-        <v>-1.531886577509751</v>
+        <v>0.9075220085576159</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.762474789192293</v>
       </c>
       <c r="E90">
-        <v>-21.9418262430208</v>
+        <v>-20.50502748139314</v>
       </c>
       <c r="F90">
-        <v>-5.283723401921293</v>
+        <v>-5.439632915904396</v>
       </c>
       <c r="G90">
-        <v>-1.593588525270687</v>
+        <v>1.306803595503574</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.905876910642771</v>
       </c>
       <c r="E91">
-        <v>-24.47972798808751</v>
+        <v>-22.37414154263706</v>
       </c>
       <c r="F91">
-        <v>-5.113131904090971</v>
+        <v>-5.354715316708613</v>
       </c>
       <c r="G91">
-        <v>-1.023307329584754</v>
+        <v>0.6444693705526666</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.06998068421791</v>
       </c>
       <c r="E92">
-        <v>-25.47760893499573</v>
+        <v>-25.24753075608802</v>
       </c>
       <c r="F92">
-        <v>-5.248952680188784</v>
+        <v>-5.51365582701856</v>
       </c>
       <c r="G92">
-        <v>-1.547323651359373</v>
+        <v>0.7405149177380023</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.249087043725618</v>
       </c>
       <c r="E93">
-        <v>-27.5420541940865</v>
+        <v>-27.35331645439481</v>
       </c>
       <c r="F93">
-        <v>-5.273715895328072</v>
+        <v>-5.475213780956843</v>
       </c>
       <c r="G93">
-        <v>-1.897903802877113</v>
+        <v>0.3171325592661495</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.426311205211425</v>
       </c>
       <c r="E94">
-        <v>-30.6970759987855</v>
+        <v>-29.23995571004842</v>
       </c>
       <c r="F94">
-        <v>-5.432904087491456</v>
+        <v>-5.494422792660361</v>
       </c>
       <c r="G94">
-        <v>-2.153024373769968</v>
+        <v>0.3592857356176895</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.597951363714413</v>
       </c>
       <c r="E95">
-        <v>-32.31252532425275</v>
+        <v>-31.33959174065279</v>
       </c>
       <c r="F95">
-        <v>-5.482932508416129</v>
+        <v>-5.638939769752763</v>
       </c>
       <c r="G95">
-        <v>-2.394462459949016</v>
+        <v>0.1155832362897803</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.753307723642452</v>
       </c>
       <c r="E96">
-        <v>-34.07494174516495</v>
+        <v>-33.8012113410603</v>
       </c>
       <c r="F96">
-        <v>-5.440601277398269</v>
+        <v>-5.740267327198004</v>
       </c>
       <c r="G96">
-        <v>-3.094977206604338</v>
+        <v>-0.5273081547089878</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.879387912693996</v>
       </c>
       <c r="E97">
-        <v>-36.78485304693901</v>
+        <v>-36.92862983244554</v>
       </c>
       <c r="F97">
-        <v>-5.898820161563441</v>
+        <v>-5.740486844559745</v>
       </c>
       <c r="G97">
-        <v>-3.037976233509167</v>
+        <v>-0.7560205038350771</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.970644994715682</v>
       </c>
       <c r="E98">
-        <v>-39.37930863965052</v>
+        <v>-38.69203798916541</v>
       </c>
       <c r="F98">
-        <v>-5.607740139893722</v>
+        <v>-5.816529315401935</v>
       </c>
       <c r="G98">
-        <v>-3.418629380705647</v>
+        <v>-1.63200740625393</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.02470609719746</v>
       </c>
       <c r="E99">
-        <v>-42.79168135796841</v>
+        <v>-42.05922785807178</v>
       </c>
       <c r="F99">
-        <v>-6.31469538919971</v>
+        <v>-6.265399245059111</v>
       </c>
       <c r="G99">
-        <v>-3.725437499103143</v>
+        <v>-1.985646501849956</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.02387829971521</v>
       </c>
       <c r="E100">
-        <v>-44.87950486412378</v>
+        <v>-44.31622383196869</v>
       </c>
       <c r="F100">
-        <v>-5.728047251271906</v>
+        <v>-6.019447022759104</v>
       </c>
       <c r="G100">
-        <v>-4.270647933420176</v>
+        <v>-2.695556576745731</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.986426558322593</v>
       </c>
       <c r="E101">
-        <v>-47.52419481900237</v>
+        <v>-47.45251813240897</v>
       </c>
       <c r="F101">
-        <v>-6.089073788066611</v>
+        <v>-6.217011819959383</v>
       </c>
       <c r="G101">
-        <v>-5.146518966745154</v>
+        <v>-2.895175851672704</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.884966923021365</v>
       </c>
       <c r="E102">
-        <v>-49.73736535357155</v>
+        <v>-49.38801396201282</v>
       </c>
       <c r="F102">
-        <v>-5.808844551006164</v>
+        <v>-6.107345916237563</v>
       </c>
       <c r="G102">
-        <v>-5.568663181185319</v>
+        <v>-3.461249343978224</v>
       </c>
     </row>
   </sheetData>
